--- a/poker/resources/sample/ImmortalHand.xlsx
+++ b/poker/resources/sample/ImmortalHand.xlsx
@@ -1122,6 +1122,9 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D5" s="1">
+        <v>300800022</v>
+      </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -1139,6 +1142,9 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D6" s="1">
+        <v>300800023</v>
+      </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
@@ -1156,6 +1162,9 @@
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D7" s="1">
+        <v>300800024</v>
+      </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
@@ -1173,6 +1182,9 @@
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="D8" s="1">
+        <v>300800025</v>
+      </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
@@ -1190,6 +1202,9 @@
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D9" s="1">
+        <v>300800026</v>
+      </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
@@ -1207,6 +1222,9 @@
       <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="D10" s="1">
+        <v>300800027</v>
+      </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
@@ -1224,6 +1242,9 @@
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D11" s="1">
+        <v>300800028</v>
+      </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
@@ -1241,6 +1262,9 @@
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D12" s="1">
+        <v>300800029</v>
+      </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
@@ -1258,6 +1282,9 @@
       <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D13" s="1">
+        <v>300800030</v>
+      </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
@@ -1275,6 +1302,9 @@
       <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D14" s="1">
+        <v>300800031</v>
+      </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
@@ -1292,6 +1322,9 @@
       <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D15" s="1">
+        <v>300800026</v>
+      </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
@@ -1309,6 +1342,9 @@
       <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="D16" s="1">
+        <v>300800032</v>
+      </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
@@ -1326,6 +1362,9 @@
       <c r="C17" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D17" s="1">
+        <v>300800033</v>
+      </c>
       <c r="E17" s="1">
         <v>5</v>
       </c>
@@ -1343,6 +1382,9 @@
       <c r="C18" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="D18" s="1">
+        <v>300800034</v>
+      </c>
       <c r="E18" s="1">
         <v>5</v>
       </c>
@@ -1360,6 +1402,9 @@
       <c r="C19" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="D19" s="1">
+        <v>300800035</v>
+      </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
@@ -1377,6 +1422,9 @@
       <c r="C20" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="D20" s="1">
+        <v>300800036</v>
+      </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
@@ -1394,6 +1442,9 @@
       <c r="C21" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D21" s="1">
+        <v>300800028</v>
+      </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
@@ -1411,6 +1462,9 @@
       <c r="C22" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D22" s="1">
+        <v>300800037</v>
+      </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
@@ -1428,6 +1482,9 @@
       <c r="C23" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D23" s="1">
+        <v>300800023</v>
+      </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
@@ -1444,6 +1501,9 @@
       </c>
       <c r="C24" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="D24" s="1">
+        <v>300800026</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
